--- a/data/trans_orig/IP05A04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP05A04-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83452</t>
+          <t>83469</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95446</t>
+          <t>95088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78577</t>
+          <t>78713</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88855</t>
+          <t>88815</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166289</t>
+          <t>165911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181290</t>
+          <t>181665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>18488</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>14555</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>29344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71375</t>
+          <t>72012</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80664</t>
+          <t>80625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71941</t>
+          <t>71568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80076</t>
+          <t>80182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146345</t>
+          <t>146333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158724</t>
+          <t>158887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20277</t>
+          <t>20385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53237</t>
+          <t>52593</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61728</t>
+          <t>61766</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85436</t>
+          <t>85422</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94697</t>
+          <t>94275</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>142842</t>
+          <t>141869</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>154952</t>
+          <t>154533</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11314</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>159567</t>
+          <t>159247</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175715</t>
+          <t>175829</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>175386</t>
+          <t>174332</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187948</t>
+          <t>188323</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>339612</t>
+          <t>339369</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>361203</t>
+          <t>359702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>18008</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32988</t>
+          <t>33265</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24229</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32536</t>
+          <t>33513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>53224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84567</t>
+          <t>84693</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95229</t>
+          <t>95112</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97767</t>
+          <t>97816</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111555</t>
+          <t>111013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>186030</t>
+          <t>187249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>203634</t>
+          <t>204266</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23400</t>
+          <t>23065</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19493</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>35647</t>
+          <t>34886</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>12077</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>63250</t>
+          <t>62957</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70969</t>
+          <t>70852</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61760</t>
+          <t>61688</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69071</t>
+          <t>69109</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>127528</t>
+          <t>127057</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>138668</t>
+          <t>138154</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2463</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15940</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>537186</t>
+          <t>537745</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>564340</t>
+          <t>564481</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>593389</t>
+          <t>593788</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>617951</t>
+          <t>618909</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1138327</t>
+          <t>1138608</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1174350</t>
+          <t>1177209</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>55556</t>
+          <t>55448</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>80960</t>
+          <t>81429</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>48716</t>
+          <t>48039</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>71630</t>
+          <t>71366</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>110489</t>
+          <t>108496</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>144985</t>
+          <t>144308</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20201</t>
+          <t>20305</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17323</t>
+          <t>17210</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>33505</t>
+          <t>34176</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75412</t>
+          <t>75554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85033</t>
+          <t>84965</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74767</t>
+          <t>74897</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84368</t>
+          <t>84801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154839</t>
+          <t>154371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167925</t>
+          <t>167645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16484</t>
+          <t>16212</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>769</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12990</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79392</t>
+          <t>79613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88824</t>
+          <t>88848</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>86147</t>
+          <t>86453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94004</t>
+          <t>93992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169571</t>
+          <t>169218</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181496</t>
+          <t>181498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>18279</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73062</t>
+          <t>72890</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82065</t>
+          <t>81963</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79763</t>
+          <t>79810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85668</t>
+          <t>85658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>156054</t>
+          <t>155916</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>166374</t>
+          <t>166389</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12361</t>
+          <t>12533</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15351</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>185400</t>
+          <t>186171</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197485</t>
+          <t>197428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>192421</t>
+          <t>192590</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>208499</t>
+          <t>208362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>383015</t>
+          <t>381958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>403347</t>
+          <t>402950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17421</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32406</t>
+          <t>32287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>45441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132022</t>
+          <t>132777</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>141889</t>
+          <t>141916</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125514</t>
+          <t>125569</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>135614</t>
+          <t>135424</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>261224</t>
+          <t>261552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>275293</t>
+          <t>275322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13206</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22489</t>
+          <t>22649</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47262</t>
+          <t>47483</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53129</t>
+          <t>53222</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62014</t>
+          <t>61846</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69761</t>
+          <t>69715</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>112291</t>
+          <t>112114</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>121861</t>
+          <t>121345</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11123</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>614391</t>
+          <t>615079</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>636655</t>
+          <t>636211</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>641196</t>
+          <t>642113</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>665589</t>
+          <t>666822</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1263802</t>
+          <t>1264979</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1296298</t>
+          <t>1296515</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28740</t>
+          <t>28604</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47628</t>
+          <t>47467</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40687</t>
+          <t>38729</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61519</t>
+          <t>61574</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>72703</t>
+          <t>72281</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>102929</t>
+          <t>101362</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17950</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16582</t>
+          <t>15691</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14170</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>29022</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74565</t>
+          <t>74769</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81036</t>
+          <t>81151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87955</t>
+          <t>88111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96087</t>
+          <t>95939</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165789</t>
+          <t>166021</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>176035</t>
+          <t>175762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>572</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92337</t>
+          <t>91692</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100732</t>
+          <t>100489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96020</t>
+          <t>96186</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106555</t>
+          <t>106391</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191924</t>
+          <t>192412</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204749</t>
+          <t>205613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15869</t>
+          <t>16063</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10458</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22325</t>
+          <t>21993</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50148</t>
+          <t>49986</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58182</t>
+          <t>58007</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63662</t>
+          <t>63191</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71936</t>
+          <t>71917</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>117373</t>
+          <t>115948</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127963</t>
+          <t>128093</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9556</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>11585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>564</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>191096</t>
+          <t>191493</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>206205</t>
+          <t>205580</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>175290</t>
+          <t>175604</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>191211</t>
+          <t>191207</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>372224</t>
+          <t>373072</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>393826</t>
+          <t>393712</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23665</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23966</t>
+          <t>23159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25082</t>
+          <t>24405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43239</t>
+          <t>41901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11863</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>24948</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>118704</t>
+          <t>118535</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129056</t>
+          <t>128686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>124610</t>
+          <t>122978</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>134790</t>
+          <t>134375</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>247526</t>
+          <t>247184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>260982</t>
+          <t>261540</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14704</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>11508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>23460</t>
+          <t>23185</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45286</t>
+          <t>45113</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54176</t>
+          <t>54147</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50909</t>
+          <t>50640</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61001</t>
+          <t>60798</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>99574</t>
+          <t>98803</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>113720</t>
+          <t>112854</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>12531</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18187</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>591907</t>
+          <t>593061</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>616324</t>
+          <t>616762</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>621847</t>
+          <t>620990</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>647633</t>
+          <t>647509</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1220446</t>
+          <t>1220834</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1256747</t>
+          <t>1256843</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35214</t>
+          <t>34558</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56012</t>
+          <t>54950</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>39640</t>
+          <t>40278</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>62926</t>
+          <t>63383</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>81244</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>111299</t>
+          <t>111935</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25984</t>
+          <t>24590</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>14417</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>29839</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>29661</t>
+          <t>29580</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>48172</t>
+          <t>48855</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97692</t>
+          <t>98182</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103336</t>
+          <t>103349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126923</t>
+          <t>126249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134361</t>
+          <t>134322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>228315</t>
+          <t>227709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>237010</t>
+          <t>237037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82231</t>
+          <t>82989</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91121</t>
+          <t>91375</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87636</t>
+          <t>88189</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94767</t>
+          <t>94724</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173971</t>
+          <t>174244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184802</t>
+          <t>184547</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45757</t>
+          <t>45228</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51138</t>
+          <t>51161</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54857</t>
+          <t>56402</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62801</t>
+          <t>62692</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104737</t>
+          <t>104393</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112942</t>
+          <t>113071</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>207887</t>
+          <t>208311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>215559</t>
+          <t>215855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>197336</t>
+          <t>198266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>211397</t>
+          <t>211152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>410152</t>
+          <t>408979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>424847</t>
+          <t>424640</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>13148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17546</t>
+          <t>17766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14729</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105840</t>
+          <t>106024</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115153</t>
+          <t>115334</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>148148</t>
+          <t>147997</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159732</t>
+          <t>159614</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>258903</t>
+          <t>258980</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>273977</t>
+          <t>273300</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>420</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61328</t>
+          <t>61315</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67707</t>
+          <t>67733</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62861</t>
+          <t>62314</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>70050</t>
+          <t>69986</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>126871</t>
+          <t>126946</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>136521</t>
+          <t>136384</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>619115</t>
+          <t>619245</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>636994</t>
+          <t>636324</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>700676</t>
+          <t>701167</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>723411</t>
+          <t>723129</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1325900</t>
+          <t>1325988</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1355721</t>
+          <t>1354330</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11751</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25638</t>
+          <t>25827</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16641</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35960</t>
+          <t>35025</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32503</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>56561</t>
+          <t>55583</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14733</t>
+          <t>15349</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>11363</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>28271</t>
+          <t>27291</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
